--- a/docs/design-docs/07_画面設計書_レポート.xlsx
+++ b/docs/design-docs/07_画面設計書_レポート.xlsx
@@ -10,7 +10,245 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面設計書 — 総合レポート</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>レポート</t>
+  </si>
+  <si>
+    <t>画面ID</t>
+  </si>
+  <si>
+    <t>SCR-RPT-SUMMARY-001</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>総合レポート</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-RPT-SUMMARY-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-RPT-SUMMARY-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>画面レイアウト</t>
+  </si>
+  <si>
+    <t>上部期間指定(from/to YYYYMM)/設備種別/担当班。①点検実施率推移 table形式月別graph(動的column)。目標値(95%)未満赤。②異常発生傾向 月別×異常種別cross。③設備別異常件数rank top10。CSV/印刷。</t>
+  </si>
+  <si>
+    <t>画面要素一覧</t>
+  </si>
+  <si>
+    <t>要素ID</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>入力値/選択肢</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>テスト難点タグ</t>
+  </si>
+  <si>
+    <t>rpt-rate-cell-{r}-{m}</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>実施率cell</t>
+  </si>
+  <si>
+    <t>%表示</t>
+  </si>
+  <si>
+    <t>目標未満=赤</t>
+  </si>
+  <si>
+    <t>動的column</t>
+  </si>
+  <si>
+    <t>rpt-cross-cell-{r}-{c}</t>
+  </si>
+  <si>
+    <t>cross集計cell</t>
+  </si>
+  <si>
+    <t>件数</t>
+  </si>
+  <si>
+    <t>rpt-ranking-{n}</t>
+  </si>
+  <si>
+    <t>rank行</t>
+  </si>
+  <si>
+    <t>設備名/件数</t>
+  </si>
+  <si>
+    <t>rpt-btn-print</t>
+  </si>
+  <si>
+    <t>button</t>
+  </si>
+  <si>
+    <t>印刷用表示</t>
+  </si>
+  <si>
+    <t>window.open</t>
+  </si>
+  <si>
+    <t>別window</t>
+  </si>
+  <si>
+    <t>テーブル列定義</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>ソート</t>
+  </si>
+  <si>
+    <t>月</t>
+  </si>
+  <si>
+    <t>動的</t>
+  </si>
+  <si>
+    <t>from〜to全月</t>
+  </si>
+  <si>
+    <t>設備名/異常種別</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>Struts1マッピング</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>Action Path</t>
+  </si>
+  <si>
+    <t>/report/summary</t>
+  </si>
+  <si>
+    <t>Action Class</t>
+  </si>
+  <si>
+    <t>SummaryReportAction</t>
+  </si>
+  <si>
+    <t>Form Bean</t>
+  </si>
+  <si>
+    <t>ReportForm</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>report.summary.tiles</t>
+  </si>
+  <si>
+    <t>テスト難点詳細</t>
+  </si>
+  <si>
+    <t>動的column(期間で月数可変) header/data対応</t>
+  </si>
+  <si>
+    <t>実施率色分け(CSS)</t>
+  </si>
+  <si>
+    <t>cross集計数値正確性</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
